--- a/output/esl_schedules_2026-08-05.xlsx
+++ b/output/esl_schedules_2026-08-05.xlsx
@@ -425,23 +425,58 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C111"/>
+  <dimension ref="A1:J105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>route</t>
+          <t>Route</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>scraped_at</t>
+          <t>ETD</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Vessel</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Voyage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>POD</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ETA</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>TransitDays</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ScrapedAt</t>
         </is>
       </c>
     </row>
@@ -453,12 +488,43 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NINGBO |                                     05-Aug-2026 |                                     KHOR FAKKAN |                                     21-Aug-2026 |                                     ESL KABIR / 026C4 |                                     ECMX |                                     16 days</t>
+          <t>NINGBO</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>05-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>21-Aug-2026</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>ESL KABIR / 026C4</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>ECMX</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>16 days</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -470,12 +536,43 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NINGBO |                                     09-Aug-2026 |                                     KHOR FAKKAN |                                     26-Aug-2026 |                                     ESL KHOR FAKKAN / 026D6 |                                     EGLX |                                     17 days</t>
+          <t>NINGBO</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>09-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>26-Aug-2026</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ESL KHOR FAKKAN / 026D6</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>EGLX</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>17 days</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -487,12 +584,43 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NINGBO |                                     13-Aug-2026 |                                     KHOR FAKKAN |                                     29-Aug-2026 |                                     WIDE ALPHA / 026C6 |                                     ECMX |                                     16 days</t>
+          <t>NINGBO</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>13-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>29-Aug-2026</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>WIDE ALPHA / 026C6</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ECMX</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>16 days</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -504,12 +632,43 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NINGBO |                                     14-Aug-2026 |                                     KHOR FAKKAN |                                     02-Sep-2026 |                                     BHUDTHI BHUM / 026D7 |                                     EGLX |                                     19 days</t>
+          <t>NINGBO</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>14-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>02-Sep-2026</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>BHUDTHI BHUM / 026D7</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>EGLX</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>19 days</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -521,12 +680,43 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NINGBO |                                     21-Aug-2026 |                                     KHOR FAKKAN |                                     07-Sep-2026 |                                     KMTC COLOMBO / 026D1 |                                     ECMX |                                     17 days</t>
+          <t>NINGBO</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>21-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>07-Sep-2026</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>KMTC COLOMBO / 026D1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ECMX</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>17 days</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -538,12 +728,43 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NINGBO |                                     22-Aug-2026 |                                     KHOR FAKKAN |                                     08-Sep-2026 |                                     ESL SANA / 026D2 |                                     ECMX |                                     17 days</t>
+          <t>NINGBO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>23-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>13-Sep-2026</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>PHOEBE / 026D9</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>EGLX</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>21 days</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -555,12 +776,43 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NINGBO |                                     23-Aug-2026 |                                     KHOR FAKKAN |                                     13-Sep-2026 |                                     PHOEBE / 026D9 |                                     EGLX |                                     21 days</t>
+          <t>NINGBO</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>24-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>08-Sep-2026</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ESL SANA / 026D2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ECMX</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>15 days</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -572,12 +824,43 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NINGBO |                                     10-Sep-2026 |                                     KHOR FAKKAN |                                     25-Sep-2026 |                                     ESL KABIR / 026D4 |                                     ECMX |                                     15 days</t>
+          <t>NINGBO</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>10-Sep-2026</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>25-Sep-2026</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>ESL KABIR / 026D4</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ECMX</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>15 days</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -589,12 +872,43 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NINGBO |                                     10-Sep-2026 |                                     KHOR FAKKAN |                                     29-Sep-2026 |                                     HELLA / 026D5 |                                     ECMX |                                     19 days</t>
+          <t>NINGBO</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>10-Sep-2026</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>29-Sep-2026</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>HELLA / 026D5</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ECMX</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>19 days</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -606,12 +920,43 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NINGBO |                                     10-Sep-2026 |                                     KHOR FAKKAN |                                     27-Sep-2026 |                                     ESL NINGBO / 026E2 |                                     EGLX |                                     17 days</t>
+          <t>NINGBO</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>10-Sep-2026</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>27-Sep-2026</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>ESL NINGBO / 026E2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>EGLX</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>17 days</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -623,12 +968,43 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NINGBO |                                     13-Sep-2026 |                                     KHOR FAKKAN |                                     04-Oct-2026 |                                     ESL NHAVA SHEVA / 026E3 |                                     EGLX |                                     21 days</t>
+          <t>NINGBO</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>13-Sep-2026</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>04-Oct-2026</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ESL NHAVA SHEVA / 026E3</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>EGLX</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>21 days</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -640,12 +1016,43 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NINGBO |                                     20-Sep-2026 |                                     KHOR FAKKAN |                                     09-Oct-2026 |                                     WIDE ALPHA / 026D6 |                                     ECMX |                                     19 days</t>
+          <t>NINGBO</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>20-Sep-2026</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>09-Oct-2026</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>WIDE ALPHA / 026D6</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ECMX</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>19 days</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -657,12 +1064,43 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NINGBO |                                     27-Sep-2026 |                                     KHOR FAKKAN |                                     18-Oct-2026 |                                     ESL KHOR FAKKAN / 026E5 |                                     EGLX |                                     21 days</t>
+          <t>NINGBO</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>27-Sep-2026</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>18-Oct-2026</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ESL KHOR FAKKAN / 026E5</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>EGLX</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>21 days</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -674,12 +1112,43 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NINGBO |                                     29-Sep-2026 |                                     KHOR FAKKAN |                                     20-Oct-2026 |                                     BHUDTHI BHUM / 026E6 |                                     EGLX |                                     21 days</t>
+          <t>NINGBO</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>29-Sep-2026</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>20-Oct-2026</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>BHUDTHI BHUM / 026E6</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>EGLX</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>21 days</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -691,12 +1160,43 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NINGBO |                                     11-Oct-2026 |                                     KHOR FAKKAN |                                     01-Nov-2026 |                                     PHOEBE / 026E7 |                                     EGLX |                                     21 days</t>
+          <t>NINGBO</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>11-Oct-2026</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>01-Nov-2026</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>PHOEBE / 026E7</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>EGLX</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>21 days</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -708,12 +1208,47 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NINGBO | 	 | 05-Aug-2026 | 	ECMX	 | ESL KABIR | 	 | 026C4 | 	 | KHOR FAKKAN | 	 | 21-Aug-2026 | 	17</t>
+          <t>NINGBO</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>05-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>ECMX</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>ESL KABIR</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>026C4</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>21-Aug-2026</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -725,12 +1260,47 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NINGBO | 	 | 09-Aug-2026 | 	EGLX	 | ESL KHOR FAKKAN | 	 | 026D6 | 	 | KHOR FAKKAN | 	 | 26-Aug-2026 | 	18</t>
+          <t>NINGBO</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>09-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>EGLX</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>ESL KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>026D6</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>26-Aug-2026</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -742,12 +1312,47 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NINGBO | 	 | 13-Aug-2026 | 	ECMX	 | WIDE ALPHA | 	 | 026C6 | 	 | KHOR FAKKAN | 	 | 29-Aug-2026 | 	17</t>
+          <t>NINGBO</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>13-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>ECMX</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>WIDE ALPHA</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>026C6</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>29-Aug-2026</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -759,12 +1364,47 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NINGBO | 	 | 14-Aug-2026 | 	EGLX	 | BHUDTHI BHUM | 	 | 026D7 | 	 | KHOR FAKKAN | 	 | 02-Sep-2026 | 	20</t>
+          <t>NINGBO</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>14-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>EGLX</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>BHUDTHI BHUM</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>026D7</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>02-Sep-2026</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -776,12 +1416,47 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NINGBO | 	 | 21-Aug-2026 | 	ECMX	 | KMTC COLOMBO | 	 | 026D1 | 	 | KHOR FAKKAN | 	 | 07-Sep-2026 | 	18</t>
+          <t>NINGBO</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>21-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ECMX</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>KMTC COLOMBO</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>026D1</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>07-Sep-2026</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -793,12 +1468,47 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NINGBO | 	 | 22-Aug-2026 | 	ECMX	 | ESL SANA | 	 | 026D2 | 	 | KHOR FAKKAN | 	 | 08-Sep-2026 | 	18</t>
+          <t>NINGBO</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>23-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>EGLX</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>PHOEBE</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>026D9</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>13-Sep-2026</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -810,12 +1520,47 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NINGBO | 	 | 23-Aug-2026 | 	EGLX	 | PHOEBE | 	 | 026D9 | 	 | KHOR FAKKAN | 	 | 13-Sep-2026 | 	22</t>
+          <t>NINGBO</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>24-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ECMX</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>ESL SANA</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>026D2</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>08-Sep-2026</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -827,12 +1572,47 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NINGBO | 	 | 10-Sep-2026 | 	ECMX	 | ESL KABIR | 	 | 026D4 | 	 | KHOR FAKKAN | 	 | 25-Sep-2026 | 	16</t>
+          <t>NINGBO</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>10-Sep-2026</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ECMX</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>ESL KABIR</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>026D4</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>25-Sep-2026</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -844,12 +1624,47 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NINGBO | 	 | 10-Sep-2026 | 	ECMX	 | HELLA | 	 | 026D5 | 	 | KHOR FAKKAN | 	 | 29-Sep-2026 | 	20</t>
+          <t>NINGBO</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>10-Sep-2026</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ECMX</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>HELLA</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>026D5</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>29-Sep-2026</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -861,12 +1676,47 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NINGBO | 	 | 10-Sep-2026 | 	EGLX	 | ESL NINGBO | 	 | 026E2 | 	 | KHOR FAKKAN | 	 | 27-Sep-2026 | 	18</t>
+          <t>NINGBO</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>10-Sep-2026</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>EGLX</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>ESL NINGBO</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>026E2</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>27-Sep-2026</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -878,12 +1728,47 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NINGBO | 	 | 13-Sep-2026 | 	EGLX	 | ESL NHAVA SHEVA | 	 | 026E3 | 	 | KHOR FAKKAN | 	 | 04-Oct-2026 | 	22</t>
+          <t>NINGBO</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>13-Sep-2026</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>EGLX</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>ESL NHAVA SHEVA</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>026E3</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>04-Oct-2026</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -895,12 +1780,47 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NINGBO | 	 | 20-Sep-2026 | 	ECMX	 | WIDE ALPHA | 	 | 026D6 | 	 | KHOR FAKKAN | 	 | 09-Oct-2026 | 	20</t>
+          <t>NINGBO</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>20-Sep-2026</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ECMX</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>WIDE ALPHA</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>026D6</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>09-Oct-2026</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -912,12 +1832,47 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NINGBO | 	 | 27-Sep-2026 | 	EGLX	 | ESL KHOR FAKKAN | 	 | 026E5 | 	 | KHOR FAKKAN | 	 | 18-Oct-2026 | 	22</t>
+          <t>NINGBO</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>27-Sep-2026</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>EGLX</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>ESL KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>026E5</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>18-Oct-2026</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -929,12 +1884,47 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NINGBO | 	 | 29-Sep-2026 | 	EGLX	 | BHUDTHI BHUM | 	 | 026E6 | 	 | KHOR FAKKAN | 	 | 20-Oct-2026 | 	22</t>
+          <t>NINGBO</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>29-Sep-2026</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>EGLX</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>BHUDTHI BHUM</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>026E6</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>20-Oct-2026</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -946,12 +1936,47 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NINGBO | 	 | 11-Oct-2026 | 	EGLX	 | PHOEBE | 	 | 026E7 | 	 | KHOR FAKKAN | 	 | 01-Nov-2026 | 	22</t>
+          <t>NINGBO</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>11-Oct-2026</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>EGLX</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>PHOEBE</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>026E7</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>01-Nov-2026</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -963,12 +1988,43 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>QINGDAO |                                     04-Aug-2026 |                                     KHOR FAKKAN |                                     26-Aug-2026 |                                     ESL KHOR FAKKAN / 026D6 |                                     EGLX |                                     22 days</t>
+          <t>QINGDAO</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>04-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>26-Aug-2026</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>ESL KHOR FAKKAN / 026D6</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>EGLX</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>22 days</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -980,12 +2036,43 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>QINGDAO |                                     05-Aug-2026 |                                     PORT KLANG |                                     16-Aug-2026 |                                     TS SHANGHAI / 02631 |                                     ECSX |                                     11 days</t>
+          <t>QINGDAO</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>05-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>PORT KLANG</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>16-Aug-2026</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>TS SHANGHAI / 02631</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>ECSX</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>11 days</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -997,12 +2084,43 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PORT KLANG |                                     20-Aug-2026 |                                     KHOR FAKKAN |                                     05-Sep-2026 |                                     ESL OMAN / 02633 |                                     EVGI |                                     16 days</t>
+          <t>PORT KLANG</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>20-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>05-Sep-2026</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>ESL OMAN / 02633</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>EVGI</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>16 days</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1014,12 +2132,43 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>QINGDAO |                                     07-Aug-2026 |                                     PORT KLANG |                                     18-Aug-2026 |                                     EVER LIVING / 02630 |                                     ECSX |                                     11 days</t>
+          <t>QINGDAO</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>07-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>PORT KLANG</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>18-Aug-2026</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>EVER LIVING / 02630</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>ECSX</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>11 days</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1031,12 +2180,43 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>PORT KLANG |                                     20-Aug-2026 |                                     KHOR FAKKAN |                                     05-Sep-2026 |                                     ESL OMAN / 02633 |                                     EVGI |                                     16 days</t>
+          <t>QINGDAO</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>11-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>02-Sep-2026</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>BHUDTHI BHUM / 026D7</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>EGLX</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>22 days</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1048,12 +2228,43 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>QINGDAO |                                     11-Aug-2026 |                                     KHOR FAKKAN |                                     02-Sep-2026 |                                     BHUDTHI BHUM / 026D7 |                                     EGLX |                                     22 days</t>
+          <t>QINGDAO</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>13-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>PORT KLANG</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>23-Aug-2026</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>ITAL USODIMARE / 02632</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>ECSX</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>10 days</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1065,12 +2276,43 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>QINGDAO |                                     13-Aug-2026 |                                     PORT KLANG |                                     23-Aug-2026 |                                     ITAL USODIMARE / 02632 |                                     ECSX |                                     10 days</t>
+          <t>PORT KLANG</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>12-Sep-2026</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>ESL BUSAN / 02634</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>EVGI</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>16 days</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1082,12 +2324,43 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PORT KLANG |                                     27-Aug-2026 |                                     KHOR FAKKAN |                                     12-Sep-2026 |                                     ESL BUSAN / 02634 |                                     EVGI |                                     16 days</t>
+          <t>QINGDAO</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>21-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>13-Sep-2026</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>PHOEBE / 026D9</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>EGLX</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>23 days</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1099,12 +2372,43 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>QINGDAO |                                     21-Aug-2026 |                                     KHOR FAKKAN |                                     13-Sep-2026 |                                     PHOEBE / 026D9 |                                     EGLX |                                     23 days</t>
+          <t>QINGDAO</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>21-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>PORT KLANG</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>01-Sep-2026</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>EVER STEADY / 02633</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>ECSX</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>11 days</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1116,12 +2420,43 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>QINGDAO |                                     21-Aug-2026 |                                     PORT KLANG |                                     01-Sep-2026 |                                     EVER STEADY / 02633 |                                     ECSX |                                     11 days</t>
+          <t>PORT KLANG</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>02-Sep-2026</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>25-Sep-2026</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>ARAYA BHUM / 02630</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>EVGI</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>23 days</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1133,12 +2468,43 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PORT KLANG |                                     02-Sep-2026 |                                     KHOR FAKKAN |                                     25-Sep-2026 |                                     ARAYA BHUM / 02630 |                                     EVGI |                                     23 days</t>
+          <t>QINGDAO</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>03-Sep-2026</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>PORT KLANG</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>15-Sep-2026</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>ZHONG GU SHEN YANG / 02635</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>ECSX</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>12 days</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1150,12 +2516,43 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>QINGDAO |                                     03-Sep-2026 |                                     PORT KLANG |                                     15-Sep-2026 |                                     ZHONG GU SHEN YANG / 02635 |                                     ECSX |                                     12 days</t>
+          <t>PORT KLANG</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>17-Sep-2026</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>03-Oct-2026</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>GFS TBN / 02637</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>EVGI</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>16 days</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1167,12 +2564,43 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>PORT KLANG |                                     17-Sep-2026 |                                     KHOR FAKKAN |                                     03-Oct-2026 |                                     GFS TBN / 02637 |                                     EVGI |                                     16 days</t>
+          <t>QINGDAO</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>08-Sep-2026</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>27-Sep-2026</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>ESL NINGBO / 026E2</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>EGLX</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>19 days</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1184,12 +2612,43 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>QINGDAO |                                     08-Sep-2026 |                                     KHOR FAKKAN |                                     27-Sep-2026 |                                     ESL NINGBO / 026E2 |                                     EGLX |                                     19 days</t>
+          <t>QINGDAO</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>11-Sep-2026</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>04-Oct-2026</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>ESL NHAVA SHEVA / 026E3</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>EGLX</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>23 days</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1201,12 +2660,43 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>QINGDAO |                                     11-Sep-2026 |                                     KHOR FAKKAN |                                     04-Oct-2026 |                                     ESL NHAVA SHEVA / 026E3 |                                     EGLX |                                     23 days</t>
+          <t>QINGDAO</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>13-Sep-2026</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>PORT KLANG</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>26-Sep-2026</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>TS SHANGHAI / 02637</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>ECSX</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>13 days</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1218,12 +2708,43 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>QINGDAO |                                     13-Sep-2026 |                                     PORT KLANG |                                     26-Sep-2026 |                                     TS SHANGHAI / 02637 |                                     ECSX |                                     13 days</t>
+          <t>PORT KLANG</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>01-Oct-2026</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>17-Oct-2026</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>ESL OMAN / 02639</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>EVGI</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>16 days</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1235,12 +2756,43 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PORT KLANG |                                     01-Oct-2026 |                                     KHOR FAKKAN |                                     17-Oct-2026 |                                     ESL OMAN / 02639 |                                     EVGI |                                     16 days</t>
+          <t>QINGDAO</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>22-Sep-2026</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>PORT KLANG</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>04-Oct-2026</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>ITAL USODIMARE / 02638</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>ECSX</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>12 days</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1252,12 +2804,43 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>QINGDAO |                                     22-Sep-2026 |                                     PORT KLANG |                                     04-Oct-2026 |                                     ITAL USODIMARE / 02638 |                                     ECSX |                                     12 days</t>
+          <t>PORT KLANG</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>08-Oct-2026</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>24-Oct-2026</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>ESL BUSAN / 02640</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>EVGI</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>16 days</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1269,12 +2852,43 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PORT KLANG |                                     08-Oct-2026 |                                     KHOR FAKKAN |                                     24-Oct-2026 |                                     ESL BUSAN / 02640 |                                     EVGI |                                     16 days</t>
+          <t>QINGDAO</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>25-Sep-2026</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>18-Oct-2026</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>ESL KHOR FAKKAN / 026E5</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>EGLX</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>23 days</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1286,12 +2900,43 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>QINGDAO |                                     25-Sep-2026 |                                     KHOR FAKKAN |                                     18-Oct-2026 |                                     ESL KHOR FAKKAN / 026E5 |                                     EGLX |                                     23 days</t>
+          <t>QINGDAO</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>27-Sep-2026</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>20-Oct-2026</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>BHUDTHI BHUM / 026E6</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>EGLX</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>23 days</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1303,12 +2948,43 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>QINGDAO |                                     27-Sep-2026 |                                     KHOR FAKKAN |                                     20-Oct-2026 |                                     BHUDTHI BHUM / 026E6 |                                     EGLX |                                     23 days</t>
+          <t>QINGDAO</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>28-Sep-2026</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>PORT KLANG</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>10-Oct-2026</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>EVER STEADY / 02639</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>ECSX</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>12 days</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1320,12 +2996,43 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>QINGDAO |                                     28-Sep-2026 |                                     PORT KLANG |                                     10-Oct-2026 |                                     EVER STEADY / 02639 |                                     ECSX |                                     12 days</t>
+          <t>PORT KLANG</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>15-Oct-2026</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>31-Oct-2026</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>KMT TBN / 02641</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>EVGI</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>16 days</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1337,12 +3044,43 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PORT KLANG |                                     15-Oct-2026 |                                     KHOR FAKKAN |                                     31-Oct-2026 |                                     KMT TBN / 02641 |                                     EVGI |                                     16 days</t>
+          <t>QINGDAO</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>09-Oct-2026</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>01-Nov-2026</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>PHOEBE / 026E7</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>EGLX</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>23 days</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1354,12 +3092,47 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>QINGDAO |                                     09-Oct-2026 |                                     KHOR FAKKAN |                                     01-Nov-2026 |                                     PHOEBE / 026E7 |                                     EGLX |                                     23 days</t>
+          <t>QINGDAO</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>04-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>EGLX</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>ESL KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>026D6</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>26-Aug-2026</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1371,12 +3144,47 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>QINGDAO | 	 | 04-Aug-2026 | 	EGLX	 | ESL KHOR FAKKAN | 	 | 026D6 | 	 | KHOR FAKKAN | 	 | 26-Aug-2026 | 	23</t>
+          <t>QINGDAO</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>05-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>ECSX</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>TS SHANGHAI</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>02631</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>PORT KLANG</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>16-Aug-2026</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1388,12 +3196,47 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>QINGDAO | 	 | 05-Aug-2026 | 	ECSX	 | TS SHANGHAI | 	 | 02631 | 	 | PORT KLANG | 	 | 16-Aug-2026 | 	12</t>
+          <t>PORT KLANG</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>20-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>EVGI</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>ESL OMAN</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>02633</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>05-Sep-2026</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1405,12 +3248,47 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PORT KLANG | 	 | 20-Aug-2026 | 	EVGI	 | ESL OMAN | 	 | 02633 | 	 | KHOR FAKKAN | 	 | 05-Sep-2026 | 	17</t>
+          <t>QINGDAO</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>07-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>ECSX</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>EVER LIVING</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>02630</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>PORT KLANG</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>18-Aug-2026</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1422,12 +3300,47 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>QINGDAO | 	 | 07-Aug-2026 | 	ECSX	 | EVER LIVING | 	 | 02630 | 	 | PORT KLANG | 	 | 18-Aug-2026 | 	12</t>
+          <t>QINGDAO</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>11-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>EGLX</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>BHUDTHI BHUM</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>026D7</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>02-Sep-2026</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1439,12 +3352,47 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PORT KLANG | 	 | 20-Aug-2026 | 	EVGI	 | ESL OMAN | 	 | 02633 | 	 | KHOR FAKKAN | 	 | 05-Sep-2026 | 	17</t>
+          <t>QINGDAO</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>13-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>ECSX</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>ITAL USODIMARE</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>02632</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>PORT KLANG</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>23-Aug-2026</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1456,12 +3404,47 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>QINGDAO | 	 | 11-Aug-2026 | 	EGLX	 | BHUDTHI BHUM | 	 | 026D7 | 	 | KHOR FAKKAN | 	 | 02-Sep-2026 | 	23</t>
+          <t>PORT KLANG</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>EVGI</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>ESL BUSAN</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>02634</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>12-Sep-2026</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1473,12 +3456,47 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>QINGDAO | 	 | 13-Aug-2026 | 	ECSX	 | ITAL USODIMARE | 	 | 02632 | 	 | PORT KLANG | 	 | 23-Aug-2026 | 	11</t>
+          <t>QINGDAO</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>21-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>EGLX</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>PHOEBE</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>026D9</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>13-Sep-2026</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1490,12 +3508,47 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PORT KLANG | 	 | 27-Aug-2026 | 	EVGI	 | ESL BUSAN | 	 | 02634 | 	 | KHOR FAKKAN | 	 | 12-Sep-2026 | 	17</t>
+          <t>QINGDAO</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>21-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>ECSX</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>EVER STEADY</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>02633</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>PORT KLANG</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>01-Sep-2026</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1507,12 +3560,47 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>QINGDAO | 	 | 21-Aug-2026 | 	EGLX	 | PHOEBE | 	 | 026D9 | 	 | KHOR FAKKAN | 	 | 13-Sep-2026 | 	24</t>
+          <t>PORT KLANG</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>02-Sep-2026</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>EVGI</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>ARAYA BHUM</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>02630</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>25-Sep-2026</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1524,12 +3612,47 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>QINGDAO | 	 | 21-Aug-2026 | 	ECSX	 | EVER STEADY | 	 | 02633 | 	 | PORT KLANG | 	 | 01-Sep-2026 | 	12</t>
+          <t>QINGDAO</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>03-Sep-2026</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>ECSX</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>ZHONG GU SHEN YANG</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>02635</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>PORT KLANG</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>15-Sep-2026</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1541,12 +3664,47 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PORT KLANG | 	 | 02-Sep-2026 | 	EVGI	 | ARAYA BHUM | 	 | 02630 | 	 | KHOR FAKKAN | 	 | 25-Sep-2026 | 	24</t>
+          <t>PORT KLANG</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>17-Sep-2026</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>EVGI</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>GFS TBN</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>02637</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>03-Oct-2026</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1558,12 +3716,47 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>QINGDAO | 	 | 03-Sep-2026 | 	ECSX	 | ZHONG GU SHEN YANG | 	 | 02635 | 	 | PORT KLANG | 	 | 15-Sep-2026 | 	13</t>
+          <t>QINGDAO</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>08-Sep-2026</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>EGLX</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>ESL NINGBO</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>026E2</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>27-Sep-2026</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1575,12 +3768,47 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PORT KLANG | 	 | 17-Sep-2026 | 	EVGI	 | GFS TBN | 	 | 02637 | 	 | KHOR FAKKAN | 	 | 03-Oct-2026 | 	17</t>
+          <t>QINGDAO</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>11-Sep-2026</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>EGLX</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>ESL NHAVA SHEVA</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>026E3</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>04-Oct-2026</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1592,12 +3820,47 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>QINGDAO | 	 | 08-Sep-2026 | 	EGLX	 | ESL NINGBO | 	 | 026E2 | 	 | KHOR FAKKAN | 	 | 27-Sep-2026 | 	20</t>
+          <t>QINGDAO</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>13-Sep-2026</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>ECSX</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>TS SHANGHAI</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>02637</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>PORT KLANG</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>26-Sep-2026</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1609,12 +3872,47 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>QINGDAO | 	 | 11-Sep-2026 | 	EGLX	 | ESL NHAVA SHEVA | 	 | 026E3 | 	 | KHOR FAKKAN | 	 | 04-Oct-2026 | 	24</t>
+          <t>PORT KLANG</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>01-Oct-2026</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>EVGI</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>ESL OMAN</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>02639</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>17-Oct-2026</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1626,12 +3924,47 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>QINGDAO | 	 | 13-Sep-2026 | 	ECSX	 | TS SHANGHAI | 	 | 02637 | 	 | PORT KLANG | 	 | 26-Sep-2026 | 	14</t>
+          <t>QINGDAO</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>22-Sep-2026</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>ECSX</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>ITAL USODIMARE</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>02638</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>PORT KLANG</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>04-Oct-2026</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1643,12 +3976,47 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PORT KLANG | 	 | 01-Oct-2026 | 	EVGI	 | ESL OMAN | 	 | 02639 | 	 | KHOR FAKKAN | 	 | 17-Oct-2026 | 	17</t>
+          <t>PORT KLANG</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>08-Oct-2026</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>EVGI</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>ESL BUSAN</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>02640</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>24-Oct-2026</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1660,12 +4028,47 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>QINGDAO | 	 | 22-Sep-2026 | 	ECSX	 | ITAL USODIMARE | 	 | 02638 | 	 | PORT KLANG | 	 | 04-Oct-2026 | 	13</t>
+          <t>QINGDAO</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>25-Sep-2026</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>EGLX</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>ESL KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>026E5</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>18-Oct-2026</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1677,12 +4080,47 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>PORT KLANG | 	 | 08-Oct-2026 | 	EVGI	 | ESL BUSAN | 	 | 02640 | 	 | KHOR FAKKAN | 	 | 24-Oct-2026 | 	17</t>
+          <t>QINGDAO</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>27-Sep-2026</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>EGLX</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>BHUDTHI BHUM</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>026E6</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>20-Oct-2026</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1694,12 +4132,47 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>QINGDAO | 	 | 25-Sep-2026 | 	EGLX	 | ESL KHOR FAKKAN | 	 | 026E5 | 	 | KHOR FAKKAN | 	 | 18-Oct-2026 | 	24</t>
+          <t>QINGDAO</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>28-Sep-2026</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>ECSX</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>EVER STEADY</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>02639</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>PORT KLANG</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>10-Oct-2026</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1711,12 +4184,47 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>QINGDAO | 	 | 27-Sep-2026 | 	EGLX	 | BHUDTHI BHUM | 	 | 026E6 | 	 | KHOR FAKKAN | 	 | 20-Oct-2026 | 	24</t>
+          <t>PORT KLANG</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>15-Oct-2026</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>EVGI</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>KMT TBN</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>02641</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>31-Oct-2026</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1728,46 +4236,143 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>QINGDAO | 	 | 28-Sep-2026 | 	ECSX	 | EVER STEADY | 	 | 02639 | 	 | PORT KLANG | 	 | 10-Oct-2026 | 	13</t>
+          <t>QINGDAO</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>09-Oct-2026</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>EGLX</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>PHOEBE</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>026E7</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>01-Nov-2026</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>CNTAO→AEJEA</t>
+          <t>CNXNG→AEJEA</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>PORT KLANG | 	 | 15-Oct-2026 | 	EVGI	 | KMT TBN | 	 | 02641 | 	 | KHOR FAKKAN | 	 | 31-Oct-2026 | 	17</t>
+          <t>XINGANG</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>02-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>BUSAN</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>07-Aug-2026</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>COSCO FOS / 00431</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>FCHS</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>5 days</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>CNTAO→AEJEA</t>
+          <t>CNXNG→AEJEA</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>QINGDAO | 	 | 09-Oct-2026 | 	EGLX	 | PHOEBE | 	 | 026E7 | 	 | KHOR FAKKAN | 	 | 01-Nov-2026 | 	24</t>
+          <t>BUSAN</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-08-05 02:58 UTC</t>
+          <t>07-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>26-Aug-2026</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>ESL KHOR FAKKAN / 026D6</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>EGLX</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>19 days</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1779,12 +4384,43 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>XINGANG |                                     02-Aug-2026 |                                     BUSAN |                                     07-Aug-2026 |                                     COSCO FOS / 00431 |                                     FCHS |                                     5 days</t>
+          <t>XINGANG</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-08-05 02:59 UTC</t>
+          <t>10-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>BUSAN</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>13-Aug-2026</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>COSCO FOS / 00432</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>FCHS</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>3 days</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1796,12 +4432,43 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>BUSAN |                                     07-Aug-2026 |                                     KHOR FAKKAN |                                     26-Aug-2026 |                                     ESL KHOR FAKKAN / 026D6 |                                     EGLX |                                     19 days</t>
+          <t>BUSAN</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-08-05 02:59 UTC</t>
+          <t>18-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>13-Sep-2026</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>PHOEBE / 026D9</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>EGLX</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>26 days</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1813,12 +4480,47 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>XINGANG |                                     10-Aug-2026 |                                     BUSAN |                                     13-Aug-2026 |                                     COSCO FOS / 00432 |                                     FCHS |                                     3 days</t>
+          <t>XINGANG</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-08-05 02:59 UTC</t>
+          <t>02-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>FCHS</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>COSCO FOS</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>00431</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>BUSAN</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>07-Aug-2026</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1830,12 +4532,47 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>BUSAN |                                     18-Aug-2026 |                                     KHOR FAKKAN |                                     13-Sep-2026 |                                     PHOEBE / 026D9 |                                     EGLX |                                     26 days</t>
+          <t>BUSAN</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-08-05 02:59 UTC</t>
+          <t>07-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>EGLX</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>ESL KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>026D6</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>26-Aug-2026</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1847,12 +4584,47 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>XINGANG | 	 | 02-Aug-2026 | 	FCHS	 | COSCO FOS | 	 | 00431 | 	 | BUSAN | 	 | 07-Aug-2026 | 	6</t>
+          <t>XINGANG</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-08-05 02:59 UTC</t>
+          <t>10-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>FCHS</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>COSCO FOS</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>00432</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>BUSAN</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>13-Aug-2026</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
@@ -1864,46 +4636,143 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>BUSAN | 	 | 07-Aug-2026 | 	EGLX	 | ESL KHOR FAKKAN | 	 | 026D6 | 	 | KHOR FAKKAN | 	 | 26-Aug-2026 | 	20</t>
+          <t>BUSAN</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-08-05 02:59 UTC</t>
+          <t>18-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>EGLX</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>PHOEBE</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>026D9</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>13-Sep-2026</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:26 UTC</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>CNXNG→AEJEA</t>
+          <t>CNWUH→AEJEA</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>XINGANG | 	 | 10-Aug-2026 | 	FCHS	 | COSCO FOS | 	 | 00432 | 	 | BUSAN | 	 | 13-Aug-2026 | 	4</t>
+          <t>WUHAN</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-08-05 02:59 UTC</t>
+          <t>01-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>SHANGHAI</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>09-Aug-2026</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>FEEDER / 01056</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>FCHS</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>8 days</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:27 UTC</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>CNXNG→AEJEA</t>
+          <t>CNWUH→AEJEA</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>BUSAN | 	 | 18-Aug-2026 | 	EGLX	 | PHOEBE | 	 | 026D9 | 	 | KHOR FAKKAN | 	 | 13-Sep-2026 | 	27</t>
+          <t>SHANGHAI</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026-08-05 02:59 UTC</t>
+          <t>12-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>29-Aug-2026</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>WIDE ALPHA / 026C6</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>ECMX</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>17 days</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:27 UTC</t>
         </is>
       </c>
     </row>
@@ -1915,12 +4784,43 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>WUHAN |                                     01-Aug-2026 |                                     SHANGHAI |                                     09-Aug-2026 |                                     FEEDER / 01056 |                                     FCHS |                                     8 days</t>
+          <t>WUHAN</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026-08-05 02:59 UTC</t>
+          <t>05-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>SHANGHAI</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>13-Aug-2026</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>FEEDER / 01057</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>FCHS</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>8 days</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:27 UTC</t>
         </is>
       </c>
     </row>
@@ -1932,12 +4832,43 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SHANGHAI |                                     12-Aug-2026 |                                     KHOR FAKKAN |                                     29-Aug-2026 |                                     WIDE ALPHA / 026C6 |                                     ECMX |                                     17 days</t>
+          <t>SHANGHAI</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026-08-05 02:59 UTC</t>
+          <t>19-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>07-Sep-2026</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>KMTC COLOMBO / 026D1</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>ECMX</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>19 days</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:27 UTC</t>
         </is>
       </c>
     </row>
@@ -1949,12 +4880,43 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>WUHAN |                                     05-Aug-2026 |                                     SHANGHAI |                                     13-Aug-2026 |                                     FEEDER / 01057 |                                     FCHS |                                     8 days</t>
+          <t>WUHAN</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026-08-05 02:59 UTC</t>
+          <t>09-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>SHANGHAI</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>17-Aug-2026</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>FEEDER / 01058</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>FCHS</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>8 days</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:27 UTC</t>
         </is>
       </c>
     </row>
@@ -1966,12 +4928,43 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SHANGHAI |                                     19-Aug-2026 |                                     KHOR FAKKAN |                                     07-Sep-2026 |                                     KMTC COLOMBO / 026D1 |                                     ECMX |                                     19 days</t>
+          <t>WUHAN</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026-08-05 02:59 UTC</t>
+          <t>13-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>SHANGHAI</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>21-Aug-2026</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>FEEDER / 01059</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>FCHS</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>8 days</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:27 UTC</t>
         </is>
       </c>
     </row>
@@ -1983,12 +4976,43 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>WUHAN |                                     09-Aug-2026 |                                     SHANGHAI |                                     17-Aug-2026 |                                     FEEDER / 01058 |                                     FCHS |                                     8 days</t>
+          <t>SHANGHAI</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026-08-05 02:59 UTC</t>
+          <t>23-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>08-Sep-2026</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>ESL SANA / 026D2</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>ECMX</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>16 days</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:27 UTC</t>
         </is>
       </c>
     </row>
@@ -2000,12 +5024,43 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>SHANGHAI |                                     19-Aug-2026 |                                     KHOR FAKKAN |                                     07-Sep-2026 |                                     KMTC COLOMBO / 026D1 |                                     ECMX |                                     19 days</t>
+          <t>WUHAN</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026-08-05 02:59 UTC</t>
+          <t>17-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>SHANGHAI</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>25-Aug-2026</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>FEEDER / 01060</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>FCHS</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>8 days</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:27 UTC</t>
         </is>
       </c>
     </row>
@@ -2017,12 +5072,43 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>WUHAN |                                     13-Aug-2026 |                                     SHANGHAI |                                     21-Aug-2026 |                                     FEEDER / 01059 |                                     FCHS |                                     8 days</t>
+          <t>SHANGHAI</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026-08-05 02:59 UTC</t>
+          <t>09-Sep-2026</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>25-Sep-2026</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>ESL KABIR / 026D4</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>ECMX</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>16 days</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:27 UTC</t>
         </is>
       </c>
     </row>
@@ -2034,12 +5120,43 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SHANGHAI |                                     09-Sep-2026 |                                     KHOR FAKKAN |                                     25-Sep-2026 |                                     ESL KABIR / 026D4 |                                     ECMX |                                     16 days</t>
+          <t>WUHAN</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026-08-05 02:59 UTC</t>
+          <t>21-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>SHANGHAI</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>29-Aug-2026</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>FEEDER / 01061</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>FCHS</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>8 days</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:27 UTC</t>
         </is>
       </c>
     </row>
@@ -2051,12 +5168,47 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>WUHAN |                                     17-Aug-2026 |                                     SHANGHAI |                                     25-Aug-2026 |                                     FEEDER / 01060 |                                     FCHS |                                     8 days</t>
+          <t>WUHAN</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026-08-05 02:59 UTC</t>
+          <t>01-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>FCHS</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>FEEDER</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>01056</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>SHANGHAI</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>09-Aug-2026</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:27 UTC</t>
         </is>
       </c>
     </row>
@@ -2068,12 +5220,47 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SHANGHAI |                                     09-Sep-2026 |                                     KHOR FAKKAN |                                     25-Sep-2026 |                                     ESL KABIR / 026D4 |                                     ECMX |                                     16 days</t>
+          <t>SHANGHAI</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026-08-05 02:59 UTC</t>
+          <t>12-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>ECMX</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>WIDE ALPHA</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>026C6</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>29-Aug-2026</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:27 UTC</t>
         </is>
       </c>
     </row>
@@ -2085,12 +5272,47 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>WUHAN |                                     21-Aug-2026 |                                     SHANGHAI |                                     29-Aug-2026 |                                     FEEDER / 01061 |                                     FCHS |                                     8 days</t>
+          <t>WUHAN</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026-08-05 02:59 UTC</t>
+          <t>05-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>FCHS</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>FEEDER</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>01057</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>SHANGHAI</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>13-Aug-2026</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:27 UTC</t>
         </is>
       </c>
     </row>
@@ -2102,12 +5324,47 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>SHANGHAI |                                     09-Sep-2026 |                                     KHOR FAKKAN |                                     25-Sep-2026 |                                     ESL KABIR / 026D4 |                                     ECMX |                                     16 days</t>
+          <t>SHANGHAI</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026-08-05 02:59 UTC</t>
+          <t>19-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>ECMX</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>KMTC COLOMBO</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>026D1</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>07-Sep-2026</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:27 UTC</t>
         </is>
       </c>
     </row>
@@ -2119,12 +5376,47 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>WUHAN | 	 | 01-Aug-2026 | 	FCHS	 | FEEDER | 	 | 01056 | 	 | SHANGHAI | 	 | 09-Aug-2026 | 	9</t>
+          <t>WUHAN</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026-08-05 02:59 UTC</t>
+          <t>09-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>FCHS</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>FEEDER</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>01058</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>SHANGHAI</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>17-Aug-2026</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:27 UTC</t>
         </is>
       </c>
     </row>
@@ -2136,12 +5428,47 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>SHANGHAI | 	 | 12-Aug-2026 | 	ECMX	 | WIDE ALPHA | 	 | 026C6 | 	 | KHOR FAKKAN | 	 | 29-Aug-2026 | 	18</t>
+          <t>WUHAN</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026-08-05 02:59 UTC</t>
+          <t>13-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>FCHS</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>FEEDER</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>01059</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>SHANGHAI</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>21-Aug-2026</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:27 UTC</t>
         </is>
       </c>
     </row>
@@ -2153,12 +5480,47 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>WUHAN | 	 | 05-Aug-2026 | 	FCHS	 | FEEDER | 	 | 01057 | 	 | SHANGHAI | 	 | 13-Aug-2026 | 	9</t>
+          <t>SHANGHAI</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026-08-05 02:59 UTC</t>
+          <t>23-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>ECMX</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>ESL SANA</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>026D2</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>08-Sep-2026</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:27 UTC</t>
         </is>
       </c>
     </row>
@@ -2170,12 +5532,47 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>SHANGHAI | 	 | 19-Aug-2026 | 	ECMX	 | KMTC COLOMBO | 	 | 026D1 | 	 | KHOR FAKKAN | 	 | 07-Sep-2026 | 	20</t>
+          <t>WUHAN</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026-08-05 02:59 UTC</t>
+          <t>17-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>FCHS</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>FEEDER</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>01060</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>SHANGHAI</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>25-Aug-2026</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:27 UTC</t>
         </is>
       </c>
     </row>
@@ -2187,12 +5584,47 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>WUHAN | 	 | 09-Aug-2026 | 	FCHS	 | FEEDER | 	 | 01058 | 	 | SHANGHAI | 	 | 17-Aug-2026 | 	9</t>
+          <t>SHANGHAI</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026-08-05 02:59 UTC</t>
+          <t>09-Sep-2026</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>ECMX</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>ESL KABIR</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>026D4</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>25-Sep-2026</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:27 UTC</t>
         </is>
       </c>
     </row>
@@ -2204,114 +5636,47 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>SHANGHAI | 	 | 19-Aug-2026 | 	ECMX	 | KMTC COLOMBO | 	 | 026D1 | 	 | KHOR FAKKAN | 	 | 07-Sep-2026 | 	20</t>
+          <t>WUHAN</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026-08-05 02:59 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>CNWUH→AEJEA</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>WUHAN | 	 | 13-Aug-2026 | 	FCHS	 | FEEDER | 	 | 01059 | 	 | SHANGHAI | 	 | 21-Aug-2026 | 	9</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>2026-08-05 02:59 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>CNWUH→AEJEA</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>SHANGHAI | 	 | 09-Sep-2026 | 	ECMX	 | ESL KABIR | 	 | 026D4 | 	 | KHOR FAKKAN | 	 | 25-Sep-2026 | 	17</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>2026-08-05 02:59 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>CNWUH→AEJEA</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>WUHAN | 	 | 17-Aug-2026 | 	FCHS	 | FEEDER | 	 | 01060 | 	 | SHANGHAI | 	 | 25-Aug-2026 | 	9</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>2026-08-05 02:59 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>CNWUH→AEJEA</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>SHANGHAI | 	 | 09-Sep-2026 | 	ECMX	 | ESL KABIR | 	 | 026D4 | 	 | KHOR FAKKAN | 	 | 25-Sep-2026 | 	17</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>2026-08-05 02:59 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>CNWUH→AEJEA</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>WUHAN | 	 | 21-Aug-2026 | 	FCHS	 | FEEDER | 	 | 01061 | 	 | SHANGHAI | 	 | 29-Aug-2026 | 	9</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>2026-08-05 02:59 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>CNWUH→AEJEA</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>SHANGHAI | 	 | 09-Sep-2026 | 	ECMX	 | ESL KABIR | 	 | 026D4 | 	 | KHOR FAKKAN | 	 | 25-Sep-2026 | 	17</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>2026-08-05 02:59 UTC</t>
+          <t>21-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>FCHS</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>FEEDER</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>01061</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>SHANGHAI</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>29-Aug-2026</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:27 UTC</t>
         </is>
       </c>
     </row>

--- a/output/esl_schedules_2026-08-05.xlsx
+++ b/output/esl_schedules_2026-08-05.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J105"/>
+  <dimension ref="A1:J103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -524,7 +524,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -620,7 +620,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>26-Sep-2026</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -854,13 +854,13 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>15 days</t>
+          <t>16 days</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -877,7 +877,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>12-Sep-2026</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -892,23 +892,23 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>HELLA / 026D5</t>
+          <t>ESL NINGBO / 026E2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ECMX</t>
+          <t>EGLX</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>19 days</t>
+          <t>17 days</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -925,7 +925,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>13-Sep-2026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -935,12 +935,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>27-Sep-2026</t>
+          <t>04-Oct-2026</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ESL NINGBO / 026E2</t>
+          <t>ESL NHAVA SHEVA / 026E3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -950,13 +950,13 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>17 days</t>
+          <t>21 days</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>13-Sep-2026</t>
+          <t>20-Sep-2026</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -983,28 +983,28 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>04-Oct-2026</t>
+          <t>09-Oct-2026</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ESL NHAVA SHEVA / 026E3</t>
+          <t>WIDE ALPHA / 026D6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>EGLX</t>
+          <t>ECMX</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>21 days</t>
+          <t>19 days</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>20-Sep-2026</t>
+          <t>27-Sep-2026</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1031,28 +1031,28 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>09-Oct-2026</t>
+          <t>18-Oct-2026</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>WIDE ALPHA / 026D6</t>
+          <t>ESL KHOR FAKKAN / 026E5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ECMX</t>
+          <t>EGLX</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>19 days</t>
+          <t>21 days</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>27-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1079,12 +1079,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>18-Oct-2026</t>
+          <t>20-Oct-2026</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ESL KHOR FAKKAN / 026E5</t>
+          <t>BHUDTHI BHUM / 026E6</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1100,7 +1100,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>11-Oct-2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1127,12 +1127,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>20-Oct-2026</t>
+          <t>01-Nov-2026</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>BHUDTHI BHUM / 026E6</t>
+          <t>PHOEBE / 026E7</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1148,7 +1148,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -1165,38 +1165,42 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>11-Oct-2026</t>
+          <t>05-Aug-2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>KHOR FAKKAN</t>
+          <t>ECMX</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>01-Nov-2026</t>
+          <t>ESL KABIR</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>PHOEBE / 026E7</t>
+          <t>026C4</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>EGLX</t>
+          <t>KHOR FAKKAN</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>21 days</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>21-Aug-2026</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -1213,22 +1217,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>05-Aug-2026</t>
+          <t>09-Aug-2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ECMX</t>
+          <t>EGLX</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ESL KABIR</t>
+          <t>ESL KHOR FAKKAN</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>026C4</t>
+          <t>026D6</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1238,17 +1242,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>21-Aug-2026</t>
+          <t>26-Aug-2026</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -1265,22 +1269,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>09-Aug-2026</t>
+          <t>13-Aug-2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>EGLX</t>
+          <t>ECMX</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ESL KHOR FAKKAN</t>
+          <t>WIDE ALPHA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>026D6</t>
+          <t>026C6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1290,17 +1294,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>26-Aug-2026</t>
+          <t>29-Aug-2026</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -1317,22 +1321,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>13-Aug-2026</t>
+          <t>14-Aug-2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ECMX</t>
+          <t>EGLX</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>WIDE ALPHA</t>
+          <t>BHUDTHI BHUM</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>026C6</t>
+          <t>026D7</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1342,17 +1346,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>29-Aug-2026</t>
+          <t>02-Sep-2026</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -1369,22 +1373,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>14-Aug-2026</t>
+          <t>21-Aug-2026</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>EGLX</t>
+          <t>ECMX</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>BHUDTHI BHUM</t>
+          <t>KMTC COLOMBO</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>026D7</t>
+          <t>026D1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1394,17 +1398,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>02-Sep-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -1421,22 +1425,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>21-Aug-2026</t>
+          <t>23-Aug-2026</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ECMX</t>
+          <t>EGLX</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>KMTC COLOMBO</t>
+          <t>PHOEBE</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>026D1</t>
+          <t>026D9</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1446,17 +1450,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>13-Sep-2026</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -1473,22 +1477,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>23-Aug-2026</t>
+          <t>24-Aug-2026</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>EGLX</t>
+          <t>ECMX</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PHOEBE</t>
+          <t>ESL SANA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>026D9</t>
+          <t>026D2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1498,17 +1502,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>13-Sep-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -1525,7 +1529,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>24-Aug-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1535,12 +1539,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ESL SANA</t>
+          <t>ESL KABIR</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>026D2</t>
+          <t>026D4</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1550,17 +1554,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>26-Sep-2026</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -1577,22 +1581,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>12-Sep-2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ECMX</t>
+          <t>EGLX</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ESL KABIR</t>
+          <t>ESL NINGBO</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>026D4</t>
+          <t>026E2</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1602,17 +1606,17 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -1629,22 +1633,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>13-Sep-2026</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ECMX</t>
+          <t>EGLX</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>HELLA</t>
+          <t>ESL NHAVA SHEVA</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>026D5</t>
+          <t>026E3</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1654,17 +1658,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>04-Oct-2026</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -1681,22 +1685,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>10-Sep-2026</t>
+          <t>20-Sep-2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>EGLX</t>
+          <t>ECMX</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ESL NINGBO</t>
+          <t>WIDE ALPHA</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>026E2</t>
+          <t>026D6</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1706,17 +1710,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>27-Sep-2026</t>
+          <t>09-Oct-2026</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1737,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>13-Sep-2026</t>
+          <t>27-Sep-2026</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1743,12 +1747,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ESL NHAVA SHEVA</t>
+          <t>ESL KHOR FAKKAN</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>026E3</t>
+          <t>026E5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1758,7 +1762,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>04-Oct-2026</t>
+          <t>18-Oct-2026</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1768,7 +1772,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -1785,22 +1789,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>20-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ECMX</t>
+          <t>EGLX</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>WIDE ALPHA</t>
+          <t>BHUDTHI BHUM</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>026D6</t>
+          <t>026E6</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1810,17 +1814,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>09-Oct-2026</t>
+          <t>20-Oct-2026</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -1837,7 +1841,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>27-Sep-2026</t>
+          <t>11-Oct-2026</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1847,12 +1851,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ESL KHOR FAKKAN</t>
+          <t>PHOEBE</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>026E5</t>
+          <t>026E7</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1862,7 +1866,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>18-Oct-2026</t>
+          <t>01-Nov-2026</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1872,111 +1876,103 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CNNGB→AEJEA</t>
+          <t>CNTAO→AEJEA</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NINGBO</t>
+          <t>QINGDAO</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>29-Sep-2026</t>
+          <t>04-Aug-2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>26-Aug-2026</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>ESL KHOR FAKKAN / 026D6</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
           <t>EGLX</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>BHUDTHI BHUM</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>026E6</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>KHOR FAKKAN</t>
-        </is>
-      </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>20-Oct-2026</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
+          <t>22 days</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CNNGB→AEJEA</t>
+          <t>CNTAO→AEJEA</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NINGBO</t>
+          <t>QINGDAO</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>11-Oct-2026</t>
+          <t>05-Aug-2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>EGLX</t>
+          <t>PORT KLANG</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>PHOEBE</t>
+          <t>16-Aug-2026</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>026E7</t>
+          <t>TS SHANGHAI / 02631</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>KHOR FAKKAN</t>
+          <t>ECSX</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>01-Nov-2026</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
+          <t>11 days</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -1988,12 +1984,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>QINGDAO</t>
+          <t>PORT KLANG</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>04-Aug-2026</t>
+          <t>20-Aug-2026</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2003,28 +1999,28 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>26-Aug-2026</t>
+          <t>05-Sep-2026</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ESL KHOR FAKKAN / 026D6</t>
+          <t>ESL OMAN / 02633</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>EGLX</t>
+          <t>EVGI</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>22 days</t>
+          <t>16 days</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2037,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>05-Aug-2026</t>
+          <t>07-Aug-2026</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2051,12 +2047,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>16-Aug-2026</t>
+          <t>18-Aug-2026</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>TS SHANGHAI / 02631</t>
+          <t>EVER LIVING / 02630</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2072,7 +2068,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -2084,12 +2080,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PORT KLANG</t>
+          <t>QINGDAO</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>20-Aug-2026</t>
+          <t>11-Aug-2026</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2099,28 +2095,28 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>05-Sep-2026</t>
+          <t>02-Sep-2026</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ESL OMAN / 02633</t>
+          <t>BHUDTHI BHUM / 026D7</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>EVGI</t>
+          <t>EGLX</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>16 days</t>
+          <t>22 days</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -2137,7 +2133,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>07-Aug-2026</t>
+          <t>13-Aug-2026</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2147,12 +2143,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>18-Aug-2026</t>
+          <t>23-Aug-2026</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>EVER LIVING / 02630</t>
+          <t>ITAL USODIMARE / 02632</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2162,13 +2158,13 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>11 days</t>
+          <t>10 days</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -2180,12 +2176,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>QINGDAO</t>
+          <t>PORT KLANG</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>11-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2195,28 +2191,28 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>02-Sep-2026</t>
+          <t>12-Sep-2026</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>BHUDTHI BHUM / 026D7</t>
+          <t>ESL BUSAN / 02634</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>EGLX</t>
+          <t>EVGI</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>22 days</t>
+          <t>16 days</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -2233,38 +2229,38 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>13-Aug-2026</t>
+          <t>21-Aug-2026</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>PORT KLANG</t>
+          <t>KHOR FAKKAN</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>23-Aug-2026</t>
+          <t>13-Sep-2026</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ITAL USODIMARE / 02632</t>
+          <t>PHOEBE / 026D9</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>ECSX</t>
+          <t>EGLX</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>10 days</t>
+          <t>23 days</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -2276,43 +2272,43 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>QINGDAO</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>21-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
           <t>PORT KLANG</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>27-Aug-2026</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>KHOR FAKKAN</t>
-        </is>
-      </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>12-Sep-2026</t>
+          <t>01-Sep-2026</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>ESL BUSAN / 02634</t>
+          <t>EVER STEADY / 02633</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>EVGI</t>
+          <t>ECSX</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>16 days</t>
+          <t>11 days</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2320,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>QINGDAO</t>
+          <t>PORT KLANG</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>21-Aug-2026</t>
+          <t>02-Sep-2026</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2339,17 +2335,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>13-Sep-2026</t>
+          <t>25-Sep-2026</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>PHOEBE / 026D9</t>
+          <t>ARAYA BHUM / 02630</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>EGLX</t>
+          <t>EVGI</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2360,7 +2356,7 @@
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2373,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>21-Aug-2026</t>
+          <t>03-Sep-2026</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2387,12 +2383,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>01-Sep-2026</t>
+          <t>15-Sep-2026</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>EVER STEADY / 02633</t>
+          <t>ZHONG GU SHEN YANG / 02635</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2402,13 +2398,13 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>11 days</t>
+          <t>12 days</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -2425,7 +2421,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>02-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2435,12 +2431,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>03-Oct-2026</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>ARAYA BHUM / 02630</t>
+          <t>GFS TBN / 02637</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2450,13 +2446,13 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>23 days</t>
+          <t>16 days</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -2473,38 +2469,38 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>03-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>PORT KLANG</t>
+          <t>KHOR FAKKAN</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>ZHONG GU SHEN YANG / 02635</t>
+          <t>ESL NINGBO / 026E2</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>ECSX</t>
+          <t>EGLX</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>12 days</t>
+          <t>19 days</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -2516,12 +2512,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PORT KLANG</t>
+          <t>QINGDAO</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2531,28 +2527,28 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>03-Oct-2026</t>
+          <t>04-Oct-2026</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>GFS TBN / 02637</t>
+          <t>ESL NHAVA SHEVA / 026E3</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>EVGI</t>
+          <t>EGLX</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>16 days</t>
+          <t>23 days</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -2569,38 +2565,38 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>13-Sep-2026</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>KHOR FAKKAN</t>
+          <t>PORT KLANG</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>27-Sep-2026</t>
+          <t>26-Sep-2026</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>ESL NINGBO / 026E2</t>
+          <t>TS SHANGHAI / 02637</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>EGLX</t>
+          <t>ECSX</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>19 days</t>
+          <t>13 days</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -2612,12 +2608,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>QINGDAO</t>
+          <t>PORT KLANG</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>11-Sep-2026</t>
+          <t>01-Oct-2026</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2627,28 +2623,28 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>04-Oct-2026</t>
+          <t>17-Oct-2026</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>ESL NHAVA SHEVA / 026E3</t>
+          <t>ESL OMAN / 02639</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>EGLX</t>
+          <t>EVGI</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>23 days</t>
+          <t>16 days</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -2665,7 +2661,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>13-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2675,12 +2671,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>26-Sep-2026</t>
+          <t>04-Oct-2026</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>TS SHANGHAI / 02637</t>
+          <t>ITAL USODIMARE / 02638</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2690,13 +2686,13 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>13 days</t>
+          <t>12 days</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -2713,7 +2709,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>01-Oct-2026</t>
+          <t>08-Oct-2026</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2723,12 +2719,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>17-Oct-2026</t>
+          <t>24-Oct-2026</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>ESL OMAN / 02639</t>
+          <t>ESL BUSAN / 02640</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2744,7 +2740,7 @@
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -2761,38 +2757,38 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>22-Sep-2026</t>
+          <t>25-Sep-2026</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>PORT KLANG</t>
+          <t>KHOR FAKKAN</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>04-Oct-2026</t>
+          <t>18-Oct-2026</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>ITAL USODIMARE / 02638</t>
+          <t>ESL KHOR FAKKAN / 026E5</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>ECSX</t>
+          <t>EGLX</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>12 days</t>
+          <t>23 days</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -2804,12 +2800,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>PORT KLANG</t>
+          <t>QINGDAO</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>08-Oct-2026</t>
+          <t>27-Sep-2026</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2819,28 +2815,28 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>24-Oct-2026</t>
+          <t>20-Oct-2026</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>ESL BUSAN / 02640</t>
+          <t>BHUDTHI BHUM / 026E6</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>EVGI</t>
+          <t>EGLX</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>16 days</t>
+          <t>23 days</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -2857,38 +2853,38 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>KHOR FAKKAN</t>
+          <t>PORT KLANG</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>18-Oct-2026</t>
+          <t>10-Oct-2026</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>ESL KHOR FAKKAN / 026E5</t>
+          <t>EVER STEADY / 02639</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>EGLX</t>
+          <t>ECSX</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>23 days</t>
+          <t>12 days</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -2900,12 +2896,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>QINGDAO</t>
+          <t>PORT KLANG</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>27-Sep-2026</t>
+          <t>15-Oct-2026</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2915,28 +2911,28 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>20-Oct-2026</t>
+          <t>31-Oct-2026</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>BHUDTHI BHUM / 026E6</t>
+          <t>KMT TBN / 02641</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>EGLX</t>
+          <t>EVGI</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>23 days</t>
+          <t>16 days</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -2953,38 +2949,38 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>09-Oct-2026</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>PORT KLANG</t>
+          <t>KHOR FAKKAN</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>10-Oct-2026</t>
+          <t>01-Nov-2026</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>EVER STEADY / 02639</t>
+          <t>PHOEBE / 026E7</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>ECSX</t>
+          <t>EGLX</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>12 days</t>
+          <t>23 days</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -2996,43 +2992,47 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PORT KLANG</t>
+          <t>QINGDAO</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>15-Oct-2026</t>
+          <t>04-Aug-2026</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>KHOR FAKKAN</t>
+          <t>EGLX</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>31-Oct-2026</t>
+          <t>ESL KHOR FAKKAN</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>KMT TBN / 02641</t>
+          <t>026D6</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>EVGI</t>
+          <t>KHOR FAKKAN</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>16 days</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>26-Aug-2026</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -3049,38 +3049,42 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>09-Oct-2026</t>
+          <t>05-Aug-2026</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>KHOR FAKKAN</t>
+          <t>ECSX</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>01-Nov-2026</t>
+          <t>TS SHANGHAI</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>PHOEBE / 026E7</t>
+          <t>02631</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>EGLX</t>
+          <t>PORT KLANG</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>23 days</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>16-Aug-2026</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -3092,27 +3096,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>QINGDAO</t>
+          <t>PORT KLANG</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>04-Aug-2026</t>
+          <t>20-Aug-2026</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>EGLX</t>
+          <t>EVGI</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ESL KHOR FAKKAN</t>
+          <t>ESL OMAN</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>026D6</t>
+          <t>02633</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3122,17 +3126,17 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>26-Aug-2026</t>
+          <t>05-Sep-2026</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3153,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>05-Aug-2026</t>
+          <t>07-Aug-2026</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3159,12 +3163,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>TS SHANGHAI</t>
+          <t>EVER LIVING</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>02631</t>
+          <t>02630</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3174,7 +3178,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>16-Aug-2026</t>
+          <t>18-Aug-2026</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3184,7 +3188,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -3196,27 +3200,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PORT KLANG</t>
+          <t>QINGDAO</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>20-Aug-2026</t>
+          <t>11-Aug-2026</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>EVGI</t>
+          <t>EGLX</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>ESL OMAN</t>
+          <t>BHUDTHI BHUM</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>02633</t>
+          <t>026D7</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3226,17 +3230,17 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>05-Sep-2026</t>
+          <t>02-Sep-2026</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -3253,7 +3257,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>07-Aug-2026</t>
+          <t>13-Aug-2026</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3263,12 +3267,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>EVER LIVING</t>
+          <t>ITAL USODIMARE</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>02630</t>
+          <t>02632</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3278,17 +3282,17 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>18-Aug-2026</t>
+          <t>23-Aug-2026</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -3300,27 +3304,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>QINGDAO</t>
+          <t>PORT KLANG</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>11-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>EGLX</t>
+          <t>EVGI</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>BHUDTHI BHUM</t>
+          <t>ESL BUSAN</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>026D7</t>
+          <t>02634</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3330,17 +3334,17 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>02-Sep-2026</t>
+          <t>12-Sep-2026</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -3357,42 +3361,42 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>13-Aug-2026</t>
+          <t>21-Aug-2026</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ECSX</t>
+          <t>EGLX</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>ITAL USODIMARE</t>
+          <t>PHOEBE</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>02632</t>
+          <t>026D9</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>PORT KLANG</t>
+          <t>KHOR FAKKAN</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>23-Aug-2026</t>
+          <t>13-Sep-2026</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -3404,47 +3408,47 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
+          <t>QINGDAO</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>21-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>ECSX</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>EVER STEADY</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>02633</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
           <t>PORT KLANG</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>27-Aug-2026</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>EVGI</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>ESL BUSAN</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>02634</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>KHOR FAKKAN</t>
-        </is>
-      </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>12-Sep-2026</t>
+          <t>01-Sep-2026</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -3456,27 +3460,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>QINGDAO</t>
+          <t>PORT KLANG</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>21-Aug-2026</t>
+          <t>02-Sep-2026</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>EGLX</t>
+          <t>EVGI</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>PHOEBE</t>
+          <t>ARAYA BHUM</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>026D9</t>
+          <t>02630</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3486,7 +3490,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>13-Sep-2026</t>
+          <t>25-Sep-2026</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3496,7 +3500,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3517,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>21-Aug-2026</t>
+          <t>03-Sep-2026</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3523,12 +3527,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>EVER STEADY</t>
+          <t>ZHONG GU SHEN YANG</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>02633</t>
+          <t>02635</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3538,17 +3542,17 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>01-Sep-2026</t>
+          <t>15-Sep-2026</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -3565,7 +3569,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>02-Sep-2026</t>
+          <t>17-Sep-2026</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3575,12 +3579,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>ARAYA BHUM</t>
+          <t>GFS TBN</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>02630</t>
+          <t>02637</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3590,17 +3594,17 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>03-Oct-2026</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -3617,42 +3621,42 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>03-Sep-2026</t>
+          <t>10-Sep-2026</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ECSX</t>
+          <t>EGLX</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ZHONG GU SHEN YANG</t>
+          <t>ESL NINGBO</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>02635</t>
+          <t>026E2</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>PORT KLANG</t>
+          <t>KHOR FAKKAN</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>15-Sep-2026</t>
+          <t>29-Sep-2026</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -3664,27 +3668,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PORT KLANG</t>
+          <t>QINGDAO</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>17-Sep-2026</t>
+          <t>11-Sep-2026</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>EVGI</t>
+          <t>EGLX</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>GFS TBN</t>
+          <t>ESL NHAVA SHEVA</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>02637</t>
+          <t>026E3</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3694,17 +3698,17 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>03-Oct-2026</t>
+          <t>04-Oct-2026</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -3721,42 +3725,42 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>13-Sep-2026</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>EGLX</t>
+          <t>ECSX</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>ESL NINGBO</t>
+          <t>TS SHANGHAI</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>026E2</t>
+          <t>02637</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>KHOR FAKKAN</t>
+          <t>PORT KLANG</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>27-Sep-2026</t>
+          <t>26-Sep-2026</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -3768,27 +3772,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>QINGDAO</t>
+          <t>PORT KLANG</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>11-Sep-2026</t>
+          <t>01-Oct-2026</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>EGLX</t>
+          <t>EVGI</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>ESL NHAVA SHEVA</t>
+          <t>ESL OMAN</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>026E3</t>
+          <t>02639</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -3798,17 +3802,17 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>04-Oct-2026</t>
+          <t>17-Oct-2026</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3829,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>13-Sep-2026</t>
+          <t>22-Sep-2026</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3835,12 +3839,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>TS SHANGHAI</t>
+          <t>ITAL USODIMARE</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>02637</t>
+          <t>02638</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -3850,17 +3854,17 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>26-Sep-2026</t>
+          <t>04-Oct-2026</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -3877,7 +3881,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>01-Oct-2026</t>
+          <t>08-Oct-2026</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3887,12 +3891,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>ESL OMAN</t>
+          <t>ESL BUSAN</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>02639</t>
+          <t>02640</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -3902,7 +3906,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>17-Oct-2026</t>
+          <t>24-Oct-2026</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3912,7 +3916,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -3929,42 +3933,42 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>22-Sep-2026</t>
+          <t>25-Sep-2026</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ECSX</t>
+          <t>EGLX</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>ITAL USODIMARE</t>
+          <t>ESL KHOR FAKKAN</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>02638</t>
+          <t>026E5</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>PORT KLANG</t>
+          <t>KHOR FAKKAN</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>04-Oct-2026</t>
+          <t>18-Oct-2026</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -3976,27 +3980,27 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PORT KLANG</t>
+          <t>QINGDAO</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>08-Oct-2026</t>
+          <t>27-Sep-2026</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>EVGI</t>
+          <t>EGLX</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>ESL BUSAN</t>
+          <t>BHUDTHI BHUM</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>02640</t>
+          <t>026E6</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4006,17 +4010,17 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>24-Oct-2026</t>
+          <t>20-Oct-2026</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -4033,42 +4037,42 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>28-Sep-2026</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>EGLX</t>
+          <t>ECSX</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>ESL KHOR FAKKAN</t>
+          <t>EVER STEADY</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>026E5</t>
+          <t>02639</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>KHOR FAKKAN</t>
+          <t>PORT KLANG</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>18-Oct-2026</t>
+          <t>10-Oct-2026</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -4080,27 +4084,27 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>QINGDAO</t>
+          <t>PORT KLANG</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>27-Sep-2026</t>
+          <t>15-Oct-2026</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>EGLX</t>
+          <t>EVGI</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>BHUDTHI BHUM</t>
+          <t>KMT TBN</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>026E6</t>
+          <t>02641</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4110,17 +4114,17 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>20-Oct-2026</t>
+          <t>31-Oct-2026</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -4137,146 +4141,138 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>28-Sep-2026</t>
+          <t>09-Oct-2026</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>ECSX</t>
+          <t>EGLX</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>EVER STEADY</t>
+          <t>PHOEBE</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>02639</t>
+          <t>026E7</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>PORT KLANG</t>
+          <t>KHOR FAKKAN</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>10-Oct-2026</t>
+          <t>01-Nov-2026</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CNTAO→AEJEA</t>
+          <t>CNXNG→AEJEA</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>PORT KLANG</t>
+          <t>XINGANG</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>15-Oct-2026</t>
+          <t>02-Aug-2026</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>EVGI</t>
+          <t>BUSAN</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>KMT TBN</t>
+          <t>07-Aug-2026</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>02641</t>
+          <t>COSCO FOS / 00431</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>KHOR FAKKAN</t>
+          <t>FCHS</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>31-Oct-2026</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
+          <t>5 days</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CNTAO→AEJEA</t>
+          <t>CNXNG→AEJEA</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>QINGDAO</t>
+          <t>BUSAN</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>09-Oct-2026</t>
+          <t>07-Aug-2026</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>26-Aug-2026</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>ESL KHOR FAKKAN / 026D6</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
           <t>EGLX</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>PHOEBE</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>026E7</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>KHOR FAKKAN</t>
-        </is>
-      </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>01-Nov-2026</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
+          <t>19 days</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4289,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>02-Aug-2026</t>
+          <t>10-Aug-2026</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4303,12 +4299,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>07-Aug-2026</t>
+          <t>13-Aug-2026</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>COSCO FOS / 00431</t>
+          <t>COSCO FOS / 00432</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4318,13 +4314,13 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>5 days</t>
+          <t>3 days</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -4341,7 +4337,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>07-Aug-2026</t>
+          <t>18-Aug-2026</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4351,12 +4347,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>26-Aug-2026</t>
+          <t>13-Sep-2026</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>ESL KHOR FAKKAN / 026D6</t>
+          <t>PHOEBE / 026D9</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -4366,13 +4362,13 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>19 days</t>
+          <t>26 days</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -4389,38 +4385,42 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>10-Aug-2026</t>
+          <t>02-Aug-2026</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
+          <t>FCHS</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>COSCO FOS</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>00431</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
           <t>BUSAN</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>13-Aug-2026</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>COSCO FOS / 00432</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>FCHS</t>
-        </is>
-      </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>3 days</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>07-Aug-2026</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -4437,38 +4437,42 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>18-Aug-2026</t>
+          <t>07-Aug-2026</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>KHOR FAKKAN</t>
+          <t>EGLX</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>13-Sep-2026</t>
+          <t>ESL KHOR FAKKAN</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>PHOEBE / 026D9</t>
+          <t>026D6</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>EGLX</t>
+          <t>KHOR FAKKAN</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>26 days</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>26-Aug-2026</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -4485,7 +4489,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>02-Aug-2026</t>
+          <t>10-Aug-2026</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4500,7 +4504,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>00431</t>
+          <t>00432</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -4510,17 +4514,17 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>07-Aug-2026</t>
+          <t>13-Aug-2026</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
@@ -4537,7 +4541,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>07-Aug-2026</t>
+          <t>18-Aug-2026</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4547,12 +4551,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>ESL KHOR FAKKAN</t>
+          <t>PHOEBE</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>026D6</t>
+          <t>026D9</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -4562,121 +4566,113 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>26-Aug-2026</t>
+          <t>13-Sep-2026</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:45 UTC</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>CNXNG→AEJEA</t>
+          <t>CNWUH→AEJEA</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>XINGANG</t>
+          <t>WUHAN</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>10-Aug-2026</t>
+          <t>01-Aug-2026</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
+          <t>SHANGHAI</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>09-Aug-2026</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>FEEDER / 01056</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
           <t>FCHS</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>COSCO FOS</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>00432</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>BUSAN</t>
-        </is>
-      </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>13-Aug-2026</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>8 days</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:46 UTC</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>CNXNG→AEJEA</t>
+          <t>CNWUH→AEJEA</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>BUSAN</t>
+          <t>SHANGHAI</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>18-Aug-2026</t>
+          <t>12-Aug-2026</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>EGLX</t>
+          <t>KHOR FAKKAN</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>PHOEBE</t>
+          <t>29-Aug-2026</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>026D9</t>
+          <t>WIDE ALPHA / 026C6</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>KHOR FAKKAN</t>
+          <t>ECMX</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>13-Sep-2026</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
+          <t>17 days</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2026-08-05 03:26 UTC</t>
+          <t>2026-08-05 06:46 UTC</t>
         </is>
       </c>
     </row>
@@ -4693,7 +4689,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>01-Aug-2026</t>
+          <t>05-Aug-2026</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4703,12 +4699,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>09-Aug-2026</t>
+          <t>13-Aug-2026</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>FEEDER / 01056</t>
+          <t>FEEDER / 01057</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -4724,7 +4720,7 @@
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
-          <t>2026-08-05 03:27 UTC</t>
+          <t>2026-08-05 06:46 UTC</t>
         </is>
       </c>
     </row>
@@ -4741,7 +4737,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>12-Aug-2026</t>
+          <t>19-Aug-2026</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4751,12 +4747,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>29-Aug-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>WIDE ALPHA / 026C6</t>
+          <t>KMTC COLOMBO / 026D1</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -4766,13 +4762,13 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>17 days</t>
+          <t>19 days</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
-          <t>2026-08-05 03:27 UTC</t>
+          <t>2026-08-05 06:46 UTC</t>
         </is>
       </c>
     </row>
@@ -4789,7 +4785,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>05-Aug-2026</t>
+          <t>09-Aug-2026</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4799,12 +4795,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>13-Aug-2026</t>
+          <t>17-Aug-2026</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>FEEDER / 01057</t>
+          <t>FEEDER / 01058</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -4820,7 +4816,7 @@
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
-          <t>2026-08-05 03:27 UTC</t>
+          <t>2026-08-05 06:46 UTC</t>
         </is>
       </c>
     </row>
@@ -4832,43 +4828,43 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
+          <t>WUHAN</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>13-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
           <t>SHANGHAI</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>KHOR FAKKAN</t>
-        </is>
-      </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>21-Aug-2026</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>KMTC COLOMBO / 026D1</t>
+          <t>FEEDER / 01059</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>ECMX</t>
+          <t>FCHS</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>19 days</t>
+          <t>8 days</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
-          <t>2026-08-05 03:27 UTC</t>
+          <t>2026-08-05 06:46 UTC</t>
         </is>
       </c>
     </row>
@@ -4880,43 +4876,43 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>WUHAN</t>
+          <t>SHANGHAI</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>09-Aug-2026</t>
+          <t>23-Aug-2026</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>SHANGHAI</t>
+          <t>KHOR FAKKAN</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>17-Aug-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>FEEDER / 01058</t>
+          <t>ESL SANA / 026D2</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>FCHS</t>
+          <t>ECMX</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>8 days</t>
+          <t>16 days</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
-          <t>2026-08-05 03:27 UTC</t>
+          <t>2026-08-05 06:46 UTC</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4929,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>13-Aug-2026</t>
+          <t>17-Aug-2026</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4943,12 +4939,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>21-Aug-2026</t>
+          <t>25-Aug-2026</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>FEEDER / 01059</t>
+          <t>FEEDER / 01060</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -4964,7 +4960,7 @@
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
-          <t>2026-08-05 03:27 UTC</t>
+          <t>2026-08-05 06:46 UTC</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4977,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>23-Aug-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4991,12 +4987,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>26-Sep-2026</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>ESL SANA / 026D2</t>
+          <t>ESL KABIR / 026D4</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -5006,13 +5002,13 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>16 days</t>
+          <t>17 days</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
-          <t>2026-08-05 03:27 UTC</t>
+          <t>2026-08-05 06:46 UTC</t>
         </is>
       </c>
     </row>
@@ -5029,7 +5025,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>17-Aug-2026</t>
+          <t>21-Aug-2026</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -5039,12 +5035,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>25-Aug-2026</t>
+          <t>29-Aug-2026</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>FEEDER / 01060</t>
+          <t>FEEDER / 01061</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -5060,7 +5056,7 @@
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
-          <t>2026-08-05 03:27 UTC</t>
+          <t>2026-08-05 06:46 UTC</t>
         </is>
       </c>
     </row>
@@ -5072,43 +5068,47 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
+          <t>WUHAN</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>01-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>FCHS</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>FEEDER</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>01056</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
           <t>SHANGHAI</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>09-Sep-2026</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>KHOR FAKKAN</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>25-Sep-2026</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>ESL KABIR / 026D4</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>ECMX</t>
-        </is>
-      </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>16 days</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>09-Aug-2026</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>2026-08-05 03:27 UTC</t>
+          <t>2026-08-05 06:46 UTC</t>
         </is>
       </c>
     </row>
@@ -5120,43 +5120,47 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>WUHAN</t>
+          <t>SHANGHAI</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>21-Aug-2026</t>
+          <t>12-Aug-2026</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>SHANGHAI</t>
+          <t>ECMX</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
+          <t>WIDE ALPHA</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>026C6</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>KHOR FAKKAN</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
           <t>29-Aug-2026</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>FEEDER / 01061</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>FCHS</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>8 days</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>2026-08-05 03:27 UTC</t>
+          <t>2026-08-05 06:46 UTC</t>
         </is>
       </c>
     </row>
@@ -5173,7 +5177,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>01-Aug-2026</t>
+          <t>05-Aug-2026</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -5188,7 +5192,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>01056</t>
+          <t>01057</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -5198,7 +5202,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>09-Aug-2026</t>
+          <t>13-Aug-2026</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -5208,7 +5212,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>2026-08-05 03:27 UTC</t>
+          <t>2026-08-05 06:46 UTC</t>
         </is>
       </c>
     </row>
@@ -5225,7 +5229,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>12-Aug-2026</t>
+          <t>19-Aug-2026</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -5235,12 +5239,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>WIDE ALPHA</t>
+          <t>KMTC COLOMBO</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>026C6</t>
+          <t>026D1</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -5250,17 +5254,17 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>29-Aug-2026</t>
+          <t>07-Sep-2026</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>2026-08-05 03:27 UTC</t>
+          <t>2026-08-05 06:46 UTC</t>
         </is>
       </c>
     </row>
@@ -5277,7 +5281,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>05-Aug-2026</t>
+          <t>09-Aug-2026</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -5292,7 +5296,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>01057</t>
+          <t>01058</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -5302,7 +5306,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>13-Aug-2026</t>
+          <t>17-Aug-2026</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -5312,7 +5316,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>2026-08-05 03:27 UTC</t>
+          <t>2026-08-05 06:46 UTC</t>
         </is>
       </c>
     </row>
@@ -5324,47 +5328,47 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
+          <t>WUHAN</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>13-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>FCHS</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>FEEDER</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>01059</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
           <t>SHANGHAI</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>ECMX</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>KMTC COLOMBO</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>026D1</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>KHOR FAKKAN</t>
-        </is>
-      </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>07-Sep-2026</t>
+          <t>21-Aug-2026</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>2026-08-05 03:27 UTC</t>
+          <t>2026-08-05 06:46 UTC</t>
         </is>
       </c>
     </row>
@@ -5376,47 +5380,47 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>WUHAN</t>
+          <t>SHANGHAI</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>09-Aug-2026</t>
+          <t>23-Aug-2026</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>FCHS</t>
+          <t>ECMX</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>FEEDER</t>
+          <t>ESL SANA</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>01058</t>
+          <t>026D2</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>SHANGHAI</t>
+          <t>KHOR FAKKAN</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>17-Aug-2026</t>
+          <t>08-Sep-2026</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>2026-08-05 03:27 UTC</t>
+          <t>2026-08-05 06:46 UTC</t>
         </is>
       </c>
     </row>
@@ -5433,7 +5437,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>13-Aug-2026</t>
+          <t>17-Aug-2026</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5448,7 +5452,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>01059</t>
+          <t>01060</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -5458,7 +5462,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>21-Aug-2026</t>
+          <t>25-Aug-2026</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -5468,7 +5472,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>2026-08-05 03:27 UTC</t>
+          <t>2026-08-05 06:46 UTC</t>
         </is>
       </c>
     </row>
@@ -5485,7 +5489,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>23-Aug-2026</t>
+          <t>09-Sep-2026</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5495,12 +5499,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>ESL SANA</t>
+          <t>ESL KABIR</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>026D2</t>
+          <t>026D4</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -5510,17 +5514,17 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>08-Sep-2026</t>
+          <t>26-Sep-2026</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>2026-08-05 03:27 UTC</t>
+          <t>2026-08-05 06:46 UTC</t>
         </is>
       </c>
     </row>
@@ -5537,7 +5541,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>17-Aug-2026</t>
+          <t>21-Aug-2026</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -5552,7 +5556,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>01060</t>
+          <t>01061</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -5562,7 +5566,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>25-Aug-2026</t>
+          <t>29-Aug-2026</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -5572,111 +5576,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>2026-08-05 03:27 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>CNWUH→AEJEA</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>SHANGHAI</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>09-Sep-2026</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>ECMX</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>ESL KABIR</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>026D4</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>KHOR FAKKAN</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>25-Sep-2026</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>2026-08-05 03:27 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>CNWUH→AEJEA</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>WUHAN</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>21-Aug-2026</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>FCHS</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>FEEDER</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>01061</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>SHANGHAI</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>29-Aug-2026</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>2026-08-05 03:27 UTC</t>
+          <t>2026-08-05 06:46 UTC</t>
         </is>
       </c>
     </row>

--- a/output/esl_schedules_2026-08-05.xlsx
+++ b/output/esl_schedules_2026-08-05.xlsx
@@ -524,7 +524,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -620,7 +620,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -860,7 +860,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -1720,7 +1720,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:00 UTC</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -1972,7 +1972,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2020,7 @@
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2068,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2116,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -2164,7 +2164,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -2308,7 +2308,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -2356,7 +2356,7 @@
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -2404,7 +2404,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2452,7 @@
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -2500,7 +2500,7 @@
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -2548,7 +2548,7 @@
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2644,7 @@
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -2980,7 +2980,7 @@
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -3292,7 +3292,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -3344,7 +3344,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -3396,7 +3396,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -3500,7 +3500,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -3812,7 +3812,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3864,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -3916,7 +3916,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -3968,7 +3968,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -4072,7 +4072,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -4224,7 +4224,7 @@
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -4320,7 +4320,7 @@
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -4368,7 +4368,7 @@
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -4420,7 +4420,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2026-08-05 06:45 UTC</t>
+          <t>2026-08-05 07:01 UTC</t>
         </is>
       </c>
     </row>
@@ -4624,7 +4624,7 @@
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2026-08-05 06:46 UTC</t>
+          <t>2026-08-05 07:02 UTC</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2026-08-05 06:46 UTC</t>
+          <t>2026-08-05 07:02 UTC</t>
         </is>
       </c>
     </row>
@@ -4720,7 +4720,7 @@
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
-          <t>2026-08-05 06:46 UTC</t>
+          <t>2026-08-05 07:02 UTC</t>
         </is>
       </c>
     </row>
@@ -4768,7 +4768,7 @@
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
-          <t>2026-08-05 06:46 UTC</t>
+          <t>2026-08-05 07:02 UTC</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
-          <t>2026-08-05 06:46 UTC</t>
+          <t>2026-08-05 07:02 UTC</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
-          <t>2026-08-05 06:46 UTC</t>
+          <t>2026-08-05 07:02 UTC</t>
         </is>
       </c>
     </row>
@@ -4912,7 +4912,7 @@
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
-          <t>2026-08-05 06:46 UTC</t>
+          <t>2026-08-05 07:02 UTC</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
-          <t>2026-08-05 06:46 UTC</t>
+          <t>2026-08-05 07:02 UTC</t>
         </is>
       </c>
     </row>
@@ -5008,7 +5008,7 @@
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
-          <t>2026-08-05 06:46 UTC</t>
+          <t>2026-08-05 07:02 UTC</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5056,7 @@
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
-          <t>2026-08-05 06:46 UTC</t>
+          <t>2026-08-05 07:02 UTC</t>
         </is>
       </c>
     </row>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>2026-08-05 06:46 UTC</t>
+          <t>2026-08-05 07:02 UTC</t>
         </is>
       </c>
     </row>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>2026-08-05 06:46 UTC</t>
+          <t>2026-08-05 07:02 UTC</t>
         </is>
       </c>
     </row>
@@ -5212,7 +5212,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>2026-08-05 06:46 UTC</t>
+          <t>2026-08-05 07:02 UTC</t>
         </is>
       </c>
     </row>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>2026-08-05 06:46 UTC</t>
+          <t>2026-08-05 07:02 UTC</t>
         </is>
       </c>
     </row>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>2026-08-05 06:46 UTC</t>
+          <t>2026-08-05 07:02 UTC</t>
         </is>
       </c>
     </row>
@@ -5368,7 +5368,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>2026-08-05 06:46 UTC</t>
+          <t>2026-08-05 07:02 UTC</t>
         </is>
       </c>
     </row>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>2026-08-05 06:46 UTC</t>
+          <t>2026-08-05 07:02 UTC</t>
         </is>
       </c>
     </row>
@@ -5472,7 +5472,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>2026-08-05 06:46 UTC</t>
+          <t>2026-08-05 07:02 UTC</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>2026-08-05 06:46 UTC</t>
+          <t>2026-08-05 07:02 UTC</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>2026-08-05 06:46 UTC</t>
+          <t>2026-08-05 07:02 UTC</t>
         </is>
       </c>
     </row>

--- a/output/esl_schedules_2026-08-05.xlsx
+++ b/output/esl_schedules_2026-08-05.xlsx
@@ -524,7 +524,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:46 UTC</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:46 UTC</t>
         </is>
       </c>
     </row>
@@ -620,7 +620,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:46 UTC</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:46 UTC</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:46 UTC</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:46 UTC</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:46 UTC</t>
         </is>
       </c>
     </row>
@@ -860,7 +860,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:46 UTC</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:46 UTC</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:46 UTC</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:46 UTC</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:46 UTC</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:46 UTC</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:46 UTC</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:46 UTC</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:46 UTC</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:46 UTC</t>
         </is>
       </c>
     </row>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:46 UTC</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:46 UTC</t>
         </is>
       </c>
     </row>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:46 UTC</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:46 UTC</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:46 UTC</t>
         </is>
       </c>
     </row>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:46 UTC</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:46 UTC</t>
         </is>
       </c>
     </row>
@@ -1720,7 +1720,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:46 UTC</t>
         </is>
       </c>
     </row>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:46 UTC</t>
         </is>
       </c>
     </row>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:46 UTC</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:46 UTC</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -1972,7 +1972,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2020,7 @@
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2068,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2116,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -2164,7 +2164,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -2308,7 +2308,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>02-Sep-2026</t>
+          <t>01-Sep-2026</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>24-Sep-2026</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2356,7 +2356,7 @@
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -2404,7 +2404,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2452,7 @@
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -2500,7 +2500,7 @@
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -2548,7 +2548,7 @@
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2644,7 @@
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -2980,7 +2980,7 @@
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -3292,7 +3292,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -3344,7 +3344,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -3396,7 +3396,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>02-Sep-2026</t>
+          <t>01-Sep-2026</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>25-Sep-2026</t>
+          <t>24-Sep-2026</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -3812,7 +3812,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3864,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -3916,7 +3916,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -3968,7 +3968,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -4072,7 +4072,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -4224,7 +4224,7 @@
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -4320,7 +4320,7 @@
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -4368,7 +4368,7 @@
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -4420,7 +4420,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2026-08-05 07:41 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -4624,7 +4624,7 @@
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -4720,7 +4720,7 @@
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -4768,7 +4768,7 @@
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -4912,7 +4912,7 @@
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -5008,7 +5008,7 @@
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5056,7 @@
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -5212,7 +5212,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -5368,7 +5368,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -5472,7 +5472,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>2026-08-05 07:42 UTC</t>
+          <t>2026-08-05 07:47 UTC</t>
         </is>
       </c>
     </row>

--- a/output/esl_schedules_2026-08-05.xlsx
+++ b/output/esl_schedules_2026-08-05.xlsx
@@ -524,7 +524,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-05 07:46 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-05 07:46 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -620,7 +620,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-08-05 07:46 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-08-05 07:46 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-08-05 07:46 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-05 07:46 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-08-05 07:46 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -860,7 +860,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-08-05 07:46 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-08-05 07:46 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-08-05 07:46 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-08-05 07:46 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-08-05 07:46 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-08-05 07:46 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-08-05 07:46 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-08-05 07:46 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-08-05 07:46 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-08-05 07:46 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-08-05 07:46 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-08-05 07:46 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-08-05 07:46 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-08-05 07:46 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-08-05 07:46 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-08-05 07:46 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-08-05 07:46 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -1720,7 +1720,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-08-05 07:46 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-08-05 07:46 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-08-05 07:46 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-08-05 07:46 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -1972,7 +1972,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2020,7 @@
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2068,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2116,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -2164,7 +2164,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -2308,7 +2308,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -2356,7 +2356,7 @@
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -2404,7 +2404,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2452,7 @@
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -2500,7 +2500,7 @@
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -2548,7 +2548,7 @@
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2644,7 @@
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -2980,7 +2980,7 @@
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -3292,7 +3292,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -3344,7 +3344,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -3396,7 +3396,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -3500,7 +3500,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -3812,7 +3812,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3864,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -3916,7 +3916,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -3968,7 +3968,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -4072,7 +4072,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -4224,7 +4224,7 @@
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -4320,7 +4320,7 @@
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -4368,7 +4368,7 @@
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -4420,7 +4420,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:53 UTC</t>
         </is>
       </c>
     </row>
@@ -4624,7 +4624,7 @@
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
@@ -4720,7 +4720,7 @@
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
@@ -4768,7 +4768,7 @@
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
@@ -4912,7 +4912,7 @@
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
@@ -5008,7 +5008,7 @@
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5056,7 @@
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
@@ -5212,7 +5212,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
@@ -5368,7 +5368,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
@@ -5472,7 +5472,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>2026-08-05 07:47 UTC</t>
+          <t>2026-08-05 07:54 UTC</t>
         </is>
       </c>
     </row>
